--- a/final_data_pipeline/output/311422longform.xlsx
+++ b/final_data_pipeline/output/311422longform.xlsx
@@ -1364,7 +1364,7 @@
         <v>55</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1453,7 +1453,7 @@
         <v>55</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1542,7 +1542,7 @@
         <v>55</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1631,7 +1631,7 @@
         <v>55</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1720,7 +1720,7 @@
         <v>55</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1809,7 +1809,7 @@
         <v>55</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -1898,7 +1898,7 @@
         <v>55</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -1987,7 +1987,7 @@
         <v>55</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2076,7 +2076,7 @@
         <v>55</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2165,7 +2165,7 @@
         <v>55</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2254,7 +2254,7 @@
         <v>55</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2343,7 +2343,7 @@
         <v>55</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2432,7 +2432,7 @@
         <v>55</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2521,7 +2521,7 @@
         <v>55</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2610,7 +2610,7 @@
         <v>55</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2699,7 +2699,7 @@
         <v>55</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2788,7 +2788,7 @@
         <v>55</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -2877,7 +2877,7 @@
         <v>55</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -2966,7 +2966,7 @@
         <v>55</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB27">
         <v>8000</v>
@@ -3055,7 +3055,7 @@
         <v>55</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB28">
         <v>8000</v>
@@ -3144,7 +3144,7 @@
         <v>55</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB29">
         <v>8000</v>
@@ -3233,7 +3233,7 @@
         <v>55</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3322,7 +3322,7 @@
         <v>55</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3411,7 +3411,7 @@
         <v>55</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3500,7 +3500,7 @@
         <v>55</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3589,7 +3589,7 @@
         <v>55</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3678,7 +3678,7 @@
         <v>55</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -3767,7 +3767,7 @@
         <v>55</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB36">
         <v>8000</v>
